--- a/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-12_Submitted_Policies_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-12_Submitted_Policies_v1.0.xlsx
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>The rule that chooses the Generic or the FFY RA is to be confirmed (SP SQ06); the cases follow the demo rule.</t>
+          <t>The rule that chooses the Generic or the FFY RA is to be confirmed (SP SQ06); the cases follow the seed rule.</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>A Sold record (not eligible in the demo rules).
+          <t>A Sold record (not eligible in the seed rules).
 Data: TD-SP-05 LAMD snapshot; TD-SP-06 Rules and masters</t>
         </is>
       </c>
@@ -18347,7 +18347,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seed V1970 of the build design; firehandler and ao2 created by the test lead with their user scope</t>
+          <t>Planned seed V1970 of the build design; firehandler and ao2 created by the test lead with their user scope</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -18447,7 +18447,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seed V1971; masked rows added by the test lead</t>
+          <t>Planned seed V1971; masked rows added by the test lead</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
@@ -18467,12 +18467,12 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Active demo rule sets for sanitation, matching, classification and disposition; SM Group employee list; No Touch list; limit rule for insurer INS-MGIC Motor, maximum vehicle age 10 years; insurer rules by vehicle type (Motor) and different-from-expiring (Fire); letter rules; IAAF matrix (level 1 SBM_CHECKER, level 2 MKT_TL) and TSU matrix for TOR.</t>
+          <t>Active seed rule sets for sanitation, matching, classification and disposition; SM Group employee list; No Touch list; limit rule for insurer INS-MGIC Motor, maximum vehicle age 10 years; insurer rules by vehicle type (Motor) and different-from-expiring (Fire); letter rules; IAAF matrix (level 1 SBM_CHECKER, level 2 MKT_TL) and TSU matrix for TOR.</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seed V1970 of the build design</t>
+          <t>Planned seed V1970 of the build design</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seed V1971 of the build design</t>
+          <t>Planned seed V1971 of the build design</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seed V1972; payments keyed in Collections by the test lead</t>
+          <t>Planned seed V1972; payments keyed in Collections by the test lead</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seeds V1971-V1972; expiry dates set by the test lead</t>
+          <t>Planned seeds V1971-V1972; expiry dates set by the test lead</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
